--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="1" r:id="R0507cf53a9b745b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作品信息" sheetId="2" r:id="R70e5b81ffe1041f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选项" sheetId="3" r:id="Rb83e5d9a38f04f23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="1" r:id="R2f1bc3ed55f646c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作品信息" sheetId="2" r:id="Rd09aebdab9ec437f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选项" sheetId="3" r:id="R3b3b96d4d7844123"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -78,6 +78,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF789D8E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7FA692"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF182421"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -231,7 +241,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -327,6 +337,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -338,7 +354,7 @@
         <x:color rgb="FF275346"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDEAE4"/>
         </x:patternFill>
       </x:fill>
@@ -348,7 +364,7 @@
         <x:color rgb="FF706A60"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEEE9E0"/>
         </x:patternFill>
       </x:fill>
@@ -358,8 +374,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WorksTable" displayName="WorksTable" ref="A1:S9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="19">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WorksTable" displayName="WorksTable" ref="A1:U9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:U9"/>
+  <x:tableColumns count="21">
     <x:tableColumn id="1" name="状态"/>
     <x:tableColumn id="2" name="作品ID"/>
     <x:tableColumn id="3" name="中文名称"/>
@@ -370,7 +387,7 @@
     <x:tableColumn id="8" name="发布日期"/>
     <x:tableColumn id="9" name="更新时间"/>
     <x:tableColumn id="10" name="版本"/>
-    <x:tableColumn id="11" name="前置说明"/>
+    <x:tableColumn id="11" name="是否需要前置"/>
     <x:tableColumn id="12" name="一句话介绍"/>
     <x:tableColumn id="13" name="详细介绍"/>
     <x:tableColumn id="14" name="封面路径"/>
@@ -379,8 +396,24 @@
     <x:tableColumn id="17" name="提取码"/>
     <x:tableColumn id="18" name="原作者链接"/>
     <x:tableColumn id="19" name="是否精选"/>
+    <x:tableColumn id="20" name="放置说明"/>
+    <x:tableColumn id="21" name="前置名称/说明"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="OptionsTable" displayName="OptionsTable" ref="A1:E8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E8"/>
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="状态"/>
+    <x:tableColumn id="2" name="类别"/>
+    <x:tableColumn id="3" name="是否精选"/>
+    <x:tableColumn id="4" name="放置说明"/>
+    <x:tableColumn id="5" name="是否需要前置"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -657,6 +690,38 @@
         <x:v>不要删除表头、修改工作表名称或改变列的顺序。</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="39" t="str">
+        <x:v>放置说明</x:v>
+      </x:c>
+      <x:c r="B11" s="39" t="str">
+        <x:v>在作品信息表选择“必须放第一层”或“无需放第一层”。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="39" t="str">
+        <x:v>前置填写</x:v>
+      </x:c>
+      <x:c r="B12" s="39" t="str">
+        <x:v>先在“是否需要前置”选择“无需前置”或“需要前置”；若选择“需要前置”，再在“前置名称/说明”填写具体前置。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="39" t="str">
+        <x:v>原作者链接</x:v>
+      </x:c>
+      <x:c r="B13" s="39" t="str">
+        <x:v>填写原作者网页地址；网站详情页会把原作者姓名显示为可点击链接。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="39" t="str">
+        <x:v>汉化支持</x:v>
+      </x:c>
+      <x:c r="B14" s="39" t="str">
+        <x:v>网站固定显示“繁简汉化”，不需要在作品信息表重复填写。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
@@ -679,7 +744,7 @@
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="46" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="52" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="32" hidden="0" customWidth="1"/>
@@ -688,6 +753,8 @@
     <x:col min="17" max="17" width="12" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="38" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="12" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="15" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -722,7 +789,7 @@
         <x:v>版本</x:v>
       </x:c>
       <x:c r="K1" s="25" t="str">
-        <x:v>前置说明</x:v>
+        <x:v>是否需要前置</x:v>
       </x:c>
       <x:c r="L1" s="25" t="str">
         <x:v>一句话介绍</x:v>
@@ -747,6 +814,12 @@
       </x:c>
       <x:c r="S1" s="26" t="str">
         <x:v>是否精选</x:v>
+      </x:c>
+      <x:c r="T1" s="42" t="str">
+        <x:v>放置说明</x:v>
+      </x:c>
+      <x:c r="U1" t="str">
+        <x:v>前置名称/说明</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -799,6 +872,10 @@
       <x:c r="S2" s="31" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="T2" t="str">
+        <x:v>无需放第一层</x:v>
+      </x:c>
+      <x:c r="U2" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="27" t="str">
@@ -850,6 +927,10 @@
       <x:c r="S3" s="31" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="T3" t="str">
+        <x:v>无需放第一层</x:v>
+      </x:c>
+      <x:c r="U3" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="27" t="str">
@@ -901,6 +982,10 @@
       <x:c r="S4" s="31" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="T4" t="str">
+        <x:v>无需放第一层</x:v>
+      </x:c>
+      <x:c r="U4" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="27" t="str">
@@ -952,6 +1037,10 @@
       <x:c r="S5" s="31" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="T5" t="str">
+        <x:v>无需放第一层</x:v>
+      </x:c>
+      <x:c r="U5" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="27" t="str">
@@ -985,7 +1074,7 @@
         <x:v>原模组当前版本</x:v>
       </x:c>
       <x:c r="K6" s="28" t="str">
-        <x:v>请查看原作者说明</x:v>
+        <x:v>需要前置</x:v>
       </x:c>
       <x:c r="L6" s="30" t="str">
         <x:v>围绕年轻母亲生活展开的现实向玩法，为家庭挑战加入更多选择与故事节点。</x:v>
@@ -1003,6 +1092,12 @@
       <x:c r="S6" s="31" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="T6" t="str">
+        <x:v>无需放第一层</x:v>
+      </x:c>
+      <x:c r="U6" t="str">
+        <x:v>请查看原作者说明</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="27" t="str">
@@ -1036,7 +1131,7 @@
         <x:v>v1.0</x:v>
       </x:c>
       <x:c r="K7" s="28" t="str">
-        <x:v>请查看原作者说明</x:v>
+        <x:v>需要前置</x:v>
       </x:c>
       <x:c r="L7" s="30" t="str">
         <x:v>扩展怀孕期间的身体反应与情绪变化，让孕期体验更有层次。</x:v>
@@ -1054,6 +1149,12 @@
       <x:c r="S7" s="31" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="T7" t="str">
+        <x:v>无需放第一层</x:v>
+      </x:c>
+      <x:c r="U7" t="str">
+        <x:v>请查看原作者说明</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="27" t="str">
@@ -1087,7 +1188,7 @@
         <x:v>原模组当前版本</x:v>
       </x:c>
       <x:c r="K8" s="28" t="str">
-        <x:v>请查看原作者说明</x:v>
+        <x:v>需要前置</x:v>
       </x:c>
       <x:c r="L8" s="30" t="str">
         <x:v>通过家庭会议与成员互动，为共同生活建立更明确的规则与关系变化。</x:v>
@@ -1105,6 +1206,12 @@
       <x:c r="S8" s="31" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="T8" t="str">
+        <x:v>无需放第一层</x:v>
+      </x:c>
+      <x:c r="U8" t="str">
+        <x:v>请查看原作者说明</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="32" t="str">
@@ -1138,7 +1245,7 @@
         <x:v>原模组当前版本</x:v>
       </x:c>
       <x:c r="K9" s="33" t="str">
-        <x:v>请查看原作者说明</x:v>
+        <x:v>需要前置</x:v>
       </x:c>
       <x:c r="L9" s="35" t="str">
         <x:v>补充兄弟姐妹之间的专属互动，让手足关系拥有更细腻的亲密与摩擦。</x:v>
@@ -1156,13 +1263,19 @@
       <x:c r="S9" s="36" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="T9" t="str">
+        <x:v>无需放第一层</x:v>
+      </x:c>
+      <x:c r="U9" t="str">
+        <x:v>请查看原作者说明</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A2:A300">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="已发布"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="草稿"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="3">
+  <x:dataValidations count="5">
     <x:dataValidation type="list" sqref="A2:A300">
       <x:formula1>"草稿,待发布,已发布,已下架"</x:formula1>
     </x:dataValidation>
@@ -1172,10 +1285,16 @@
     <x:dataValidation type="list" sqref="S2:S300">
       <x:formula1>"是,否"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="T2:T200">
+      <x:formula1>'选项'!$D$2:$D$3</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="K2:K200">
+      <x:formula1>'选项'!$E$2:$E$3</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94fc1b95b9cc4e41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1149553582a4583"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1187,6 +1306,8 @@
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1199,6 +1320,12 @@
       <x:c r="C1" s="38" t="str">
         <x:v>是否精选</x:v>
       </x:c>
+      <x:c r="D1" s="41" t="str">
+        <x:v>放置说明</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>是否需要前置</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -1210,6 +1337,12 @@
       <x:c r="C2" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="D2" t="str">
+        <x:v>必须放第一层</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>无需前置</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -1220,6 +1353,12 @@
       </x:c>
       <x:c r="C3" t="str">
         <x:v>否</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>无需放第一层</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>需要前置</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1263,5 +1402,8 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2404f72ec764ed7"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -1252,7 +1252,11 @@
           <t>images/jayesims-teen-mom-reality.png</t>
         </is>
       </c>
-      <c r="K15" s="10" t="str"/>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1XabEyTJ5iDuoG-WuwboTvw 提取码: 9xvp</t>
+        </is>
+      </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
           <t>游戏玩法</t>
@@ -1306,7 +1310,11 @@
           <t>images/jayesims-cabaretconfessions.png</t>
         </is>
       </c>
-      <c r="K16" s="10" t="str"/>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1iE9y2wJsnIfwQRTvo5r4-g 提取码: r3ku</t>
+        </is>
+      </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
           <t>职业</t>
@@ -1360,7 +1368,11 @@
           <t>images/jayesims-casual-convos.png</t>
         </is>
       </c>
-      <c r="K17" s="10" t="str"/>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1ET5mLYpgXwzW4qahTCUnbA 提取码: qhq7</t>
+        </is>
+      </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
           <t>游戏玩法</t>
@@ -1414,7 +1426,11 @@
           <t>images/wicked-pixxel-sexy-gigs-v21-2.png</t>
         </is>
       </c>
-      <c r="K18" s="10" t="str"/>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1jZK0fTHBJBSLPNb7LMzu6A 提取码: ssmh</t>
+        </is>
+      </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
           <t>职业</t>
@@ -1468,7 +1484,11 @@
           <t>images/jayesims-guys-who-love-to-talk-v1.png</t>
         </is>
       </c>
-      <c r="K19" s="10" t="str"/>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1GWAdBQ_TP03V6hVzpdSI5Q 提取码: 6xrc</t>
+        </is>
+      </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
           <t>游戏玩法</t>
@@ -1522,7 +1542,11 @@
           <t>images/jayesims-householdmeeting.png</t>
         </is>
       </c>
-      <c r="K20" s="10" t="str"/>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1aOc1N2kQ7iTg2uiKJBvkDg 提取码: ay87</t>
+        </is>
+      </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
           <t>游戏玩法</t>
@@ -1576,7 +1600,11 @@
           <t>images/jayesims-girs-who-love-to-talk-v1.png</t>
         </is>
       </c>
-      <c r="K21" s="10" t="str"/>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1vAIqevOEw2Zvd_72eVuu1g 提取码: uubp</t>
+        </is>
+      </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
           <t>游戏玩法</t>
@@ -1630,7 +1658,11 @@
           <t>images/jayesims-diagnosedthechapterslupus.png</t>
         </is>
       </c>
-      <c r="K22" s="10" t="str"/>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1qMIR2l3YKPfWV_wjQN2KFg 提取码: hah2</t>
+        </is>
+      </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
           <t>游戏玩法</t>
@@ -1684,7 +1716,11 @@
           <t>images/jayesims-siblingbusiness.png</t>
         </is>
       </c>
-      <c r="K23" s="10" t="str"/>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1LbepBQlS6R-2PixF-2qSXg 提取码: 7ge8</t>
+        </is>
+      </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
           <t>游戏玩法</t>
@@ -1738,7 +1774,11 @@
           <t>images/jayesims-imyourgirl.png</t>
         </is>
       </c>
-      <c r="K24" s="10" t="str"/>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1SFcsbvp-ExYaorP8hEPqnA 提取码: 13b7</t>
+        </is>
+      </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
           <t>游戏玩法</t>
@@ -1792,7 +1832,11 @@
           <t>images/rbk-morningsicknessoverhaul-v1-0.png</t>
         </is>
       </c>
-      <c r="K25" s="10" t="str"/>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1vXR7PbTSX7KI0RbKnI2_rQ 提取码: eahu</t>
+        </is>
+      </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
           <t>覆盖替换</t>
@@ -1846,7 +1890,11 @@
           <t>images/andirz-laundromatlottrait-v-1-0-3.png</t>
         </is>
       </c>
-      <c r="K26" s="10" t="str"/>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1lzsj3v43w5DpwuRHGcBsAg 提取码: xmcj</t>
+        </is>
+      </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
           <t>用地特征</t>
@@ -1900,7 +1948,11 @@
           <t>images/jayesims-brosgonedeep.png</t>
         </is>
       </c>
-      <c r="K27" s="10" t="str"/>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1Yp9oF66mxL4VTP3k-Y048g 提取码: p4aa</t>
+        </is>
+      </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
           <t>游戏玩法</t>

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -618,7 +618,11 @@
           <t>images/klimter-hopelessromantictrait.png</t>
         </is>
       </c>
-      <c r="K4" s="10" t="str"/>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1ZAvlvcY8HZPdyl0gcs21dg 提取码: c22c</t>
+        </is>
+      </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -78,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,6 +112,7 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -384,7 +385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1963,6 +1964,60 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PeoplePleaserTrait</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>讨好型人格</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>images/klimter-peoplepleasertrait.png</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -385,7 +385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2011,8 +2011,61 @@
           <t>images/klimter-peoplepleasertrait.png</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FestiveTrait</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>节庆控</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>images/klimter-festivetrait.png</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>人物特征</t>
         </is>

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -2020,7 +2020,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已发布</t>
+          <t>待发布</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2064,7 +2064,6 @@
           <t>images/klimter-festivetrait.png</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -565,7 +565,11 @@
           <t>images/klimter-moreinfanttraits.png</t>
         </is>
       </c>
-      <c r="K3" s="10" t="str"/>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1Shof2y4VQMdnI3RnMMOmUA 提取码: dnb9</t>
+        </is>
+      </c>
       <c r="L3" s="12" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -2024,7 +2024,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>待发布</t>
+          <t>已发布</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2051,7 +2051,7 @@
         <v>46239</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>46241</v>

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -511,7 +511,11 @@
           <t>images/avathepit-aristocracy-royalty-and-mistress-careers-4-9-2.png</t>
         </is>
       </c>
-      <c r="K2" s="10" t="str"/>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1ttD1A4N_Mth-EMZjPFW9cg 提取码: 4meq</t>
+        </is>
+      </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
           <t>职业</t>

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -385,7 +385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2078,60 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MoreTeenTraits</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>更多青少年特征</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>images/klimter-moreteentraits.png</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -2019,6 +2019,11 @@
           <t>images/klimter-peoplepleasertrait.png</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1nmXL7aEQpZvDmqirQ6obrA 提取码: 8p9p</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>人物特征</t>
@@ -2125,7 +2130,6 @@
           <t>images/klimter-moreteentraits.png</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -385,7 +385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2136,6 +2136,60 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MoreSocialTraits</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>更多社交特征</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>46246</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>images/klimter-moresocialtraits.png</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -2059,8 +2059,10 @@
       <c r="F29" s="15" t="n">
         <v>46241</v>
       </c>
-      <c r="G29" s="15" t="n">
-        <v>46241</v>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2075,6 +2077,11 @@
       <c r="J29" t="inlineStr">
         <is>
           <t>images/klimter-festivetrait.png</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/16qbiUzhVnTx7oY3Du6uXEw 提取码: shrr</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2183,7 +2190,6 @@
           <t>images/klimter-moresocialtraits.png</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>人物特征</t>

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -11,8 +11,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -78,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -113,6 +114,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -385,7 +387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2196,6 +2198,59 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MoreElderTraits</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>更多老年特征</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>46248</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>images/klimter-moreeldertraits.png</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -387,7 +387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2251,59 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FoolishTrait</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>莽撞</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>46250</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <v>46250</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>images/klimter-foolishtrait.png</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -2122,7 +2122,7 @@
         <v>46244</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2137,6 +2137,11 @@
       <c r="J30" t="inlineStr">
         <is>
           <t>images/klimter-moreteentraits.png</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1JjDQCozlFUyUgMHHT4fD-g 提取码: nm5w</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -2180,7 +2180,7 @@
         <v>46246</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2195,6 +2195,11 @@
       <c r="J31" t="inlineStr">
         <is>
           <t>images/klimter-moresocialtraits.png</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>链接: https://pan.baidu.com/s/1AnvJWTbMezMBEwV_NtulzQ 提取码: i92t</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -387,7 +387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2314,6 +2314,59 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ParentalTrait</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>称职父母</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Klimter</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/cw/klimter</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>46250</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>46250</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>无需前置</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>必须放第一层</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>images/klimter-parentaltrait.png</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>人物特征</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/content/作品信息.xlsx
+++ b/content/作品信息.xlsx
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="F34" s="16" t="n">
-        <v>46250</v>
+        <v>46253</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>46250</v>
+        <v>46253</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
